--- a/engine/publish_queue/ELEC/ELEC_Valuation_Model_05082026_public.xlsx
+++ b/engine/publish_queue/ELEC/ELEC_Valuation_Model_05082026_public.xlsx
@@ -695,7 +695,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Currency. EGP million unless stated. Spot EGP 2.19 (5 Aug 2026 close). Sheets: Summary · Fundamental</t>
+          <t>Currency. EGP million unless stated. Spot EGP 2.08 (2026-09-03 close). Sheets: Summary · Fundamental</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>0.6135</v>
+        <v>0.7286</v>
       </c>
     </row>
     <row r="7">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="B7" s="43" t="inlineStr">
         <is>
-          <t>37% vs 18% · 2.1:1</t>
+          <t>50% vs 11% · 4.4:1</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="B8" s="43" t="inlineStr">
         <is>
-          <t>2.29 (+4.7%)</t>
+          <t>2.29 (+10.2%)</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="B10" s="43" t="inlineStr">
         <is>
-          <t>60% / 39%</t>
+          <t>80% / 24%</t>
         </is>
       </c>
     </row>
@@ -2024,13 +2024,13 @@
     </row>
     <row r="23">
       <c r="A23" s="39" t="n">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="B23" s="12" t="n">
-        <v>1</v>
+        <v>0.40075</v>
       </c>
       <c r="C23" s="12" t="n">
-        <v>1</v>
+        <v>0.6178</v>
       </c>
     </row>
     <row r="24">
@@ -2258,13 +2258,13 @@
         <v>0.139988</v>
       </c>
       <c r="B10" s="39" t="n">
-        <v>-1.48</v>
+        <v>-1.47</v>
       </c>
       <c r="C10" s="39" t="n">
         <v>-1.56</v>
       </c>
       <c r="D10" s="39" t="n">
-        <v>-1.68</v>
+        <v>-1.67</v>
       </c>
       <c r="E10" s="39" t="n">
         <v>-1.82</v>
@@ -2287,10 +2287,10 @@
         <v>-1.81</v>
       </c>
       <c r="E11" s="39" t="n">
-        <v>-1.95</v>
+        <v>-1.94</v>
       </c>
       <c r="F11" s="39" t="n">
-        <v>-2.13</v>
+        <v>-2.12</v>
       </c>
     </row>
     <row r="12">
@@ -2304,10 +2304,10 @@
         <v>-1.81</v>
       </c>
       <c r="D12" s="39" t="n">
-        <v>-1.92</v>
+        <v>-1.91</v>
       </c>
       <c r="E12" s="39" t="n">
-        <v>-2.05</v>
+        <v>-2.04</v>
       </c>
       <c r="F12" s="39" t="n">
         <v>-2.21</v>
@@ -2327,7 +2327,7 @@
         <v>-2</v>
       </c>
       <c r="E13" s="39" t="n">
-        <v>-2.13</v>
+        <v>-2.12</v>
       </c>
       <c r="F13" s="39" t="n">
         <v>-2.28</v>
@@ -2364,19 +2364,19 @@
     </row>
     <row r="17">
       <c r="A17" s="12" t="n">
-        <v>0.1952611846539747</v>
+        <v>0.1939056500498176</v>
       </c>
       <c r="B17" s="39" t="n">
-        <v>-1.46</v>
+        <v>-1.45</v>
       </c>
       <c r="C17" s="39" t="n">
         <v>-1.63</v>
       </c>
       <c r="D17" s="39" t="n">
-        <v>-1.77</v>
+        <v>-1.76</v>
       </c>
       <c r="E17" s="39" t="n">
-        <v>-1.88</v>
+        <v>-1.87</v>
       </c>
       <c r="F17" s="39" t="n">
         <v>-1.97</v>
@@ -2384,19 +2384,19 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="n">
-        <v>0.2052611846539747</v>
+        <v>0.2039056500498176</v>
       </c>
       <c r="B18" s="39" t="n">
-        <v>-1.49</v>
+        <v>-1.48</v>
       </c>
       <c r="C18" s="39" t="n">
         <v>-1.65</v>
       </c>
       <c r="D18" s="39" t="n">
-        <v>-1.79</v>
+        <v>-1.78</v>
       </c>
       <c r="E18" s="39" t="n">
-        <v>-1.9</v>
+        <v>-1.89</v>
       </c>
       <c r="F18" s="39" t="n">
         <v>-1.99</v>
@@ -2404,19 +2404,19 @@
     </row>
     <row r="19">
       <c r="A19" s="12" t="n">
-        <v>0.2152611846539747</v>
+        <v>0.2139056500498176</v>
       </c>
       <c r="B19" s="39" t="n">
         <v>-1.51</v>
       </c>
       <c r="C19" s="39" t="n">
-        <v>-1.68</v>
+        <v>-1.67</v>
       </c>
       <c r="D19" s="39" t="n">
         <v>-1.81</v>
       </c>
       <c r="E19" s="39" t="n">
-        <v>-1.92</v>
+        <v>-1.91</v>
       </c>
       <c r="F19" s="39" t="n">
         <v>-2</v>
@@ -2424,7 +2424,7 @@
     </row>
     <row r="20">
       <c r="A20" s="12" t="n">
-        <v>0.2252611846539747</v>
+        <v>0.2239056500498176</v>
       </c>
       <c r="B20" s="39" t="n">
         <v>-1.54</v>
@@ -2444,7 +2444,7 @@
     </row>
     <row r="21">
       <c r="A21" s="12" t="n">
-        <v>0.2352611846539747</v>
+        <v>0.2339056500498176</v>
       </c>
       <c r="B21" s="39" t="n">
         <v>-1.56</v>
@@ -2545,10 +2545,10 @@
         <v>-1.81</v>
       </c>
       <c r="E27" s="39" t="n">
-        <v>-1.57</v>
+        <v>-1.56</v>
       </c>
       <c r="F27" s="39" t="n">
-        <v>-1.33</v>
+        <v>-1.32</v>
       </c>
     </row>
     <row r="28">
@@ -2559,10 +2559,10 @@
         <v>-1.81</v>
       </c>
       <c r="C28" s="39" t="n">
-        <v>-1.57</v>
+        <v>-1.56</v>
       </c>
       <c r="D28" s="39" t="n">
-        <v>-1.33</v>
+        <v>-1.32</v>
       </c>
       <c r="E28" s="39" t="n">
         <v>-1.08</v>
@@ -2576,7 +2576,7 @@
         <v>0.3</v>
       </c>
       <c r="B29" s="39" t="n">
-        <v>-1.33</v>
+        <v>-1.32</v>
       </c>
       <c r="C29" s="39" t="n">
         <v>-1.08</v>
@@ -2585,10 +2585,10 @@
         <v>-0.84</v>
       </c>
       <c r="E29" s="39" t="n">
-        <v>-0.6</v>
+        <v>-0.59</v>
       </c>
       <c r="F29" s="39" t="n">
-        <v>-0.36</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="31">
@@ -2645,7 +2645,7 @@
         <v>6474</v>
       </c>
       <c r="D34" s="39" t="n">
-        <v>-1.9</v>
+        <v>-1.89</v>
       </c>
     </row>
     <row r="35">
@@ -2742,7 +2742,7 @@
         <v>0.24556</v>
       </c>
       <c r="C43" s="12" t="n">
-        <v>0.2012355297306375</v>
+        <v>0.2003047439516406</v>
       </c>
       <c r="D43" s="12" t="n">
         <v>0.1347</v>
@@ -2759,7 +2759,7 @@
         <v>0.262498</v>
       </c>
       <c r="C44" s="12" t="n">
-        <v>0.2081712931542658</v>
+        <v>0.2070304667474424</v>
       </c>
       <c r="D44" s="12" t="n">
         <v>0.14226</v>
@@ -2776,7 +2776,7 @@
         <v>0.26438</v>
       </c>
       <c r="C45" s="12" t="n">
-        <v>0.2089419335346689</v>
+        <v>0.2077777692803093</v>
       </c>
       <c r="D45" s="12" t="n">
         <v>0.1431</v>
@@ -2793,7 +2793,7 @@
         <v>0.2798124</v>
       </c>
       <c r="C46" s="12" t="n">
-        <v>0.2152611846539747</v>
+        <v>0.2139056500498176</v>
       </c>
       <c r="D46" s="12" t="n">
         <v>0.149988</v>
@@ -2810,13 +2810,13 @@
         <v>0.2832</v>
       </c>
       <c r="C47" s="12" t="n">
-        <v>0.2166483373387004</v>
+        <v>0.215250794608978</v>
       </c>
       <c r="D47" s="12" t="n">
         <v>0.1515</v>
       </c>
       <c r="E47" s="39" t="n">
-        <v>-1.83</v>
+        <v>-1.82</v>
       </c>
     </row>
     <row r="48">
@@ -2827,7 +2827,7 @@
         <v>0.297315</v>
       </c>
       <c r="C48" s="12" t="n">
-        <v>0.222428140191724</v>
+        <v>0.2208555636054796</v>
       </c>
       <c r="D48" s="12" t="n">
         <v>0.1578</v>
@@ -2844,7 +2844,7 @@
         <v>0.31143</v>
       </c>
       <c r="C49" s="12" t="n">
-        <v>0.2282079430447475</v>
+        <v>0.2264603326019811</v>
       </c>
       <c r="D49" s="12" t="n">
         <v>0.1641</v>
@@ -3594,7 +3594,7 @@
         <v/>
       </c>
       <c r="D6" s="7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="E6" s="9">
         <f>Assumptions!B35</f>
@@ -3955,11 +3955,11 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>5-Aug-2026 close, uploaded EGX history</t>
+          <t>2026-09-03 close, uploaded EGX history</t>
         </is>
       </c>
     </row>

--- a/engine/publish_queue/ELEC/ELEC_Valuation_Model_05082026_public.xlsx
+++ b/engine/publish_queue/ELEC/ELEC_Valuation_Model_05082026_public.xlsx
@@ -2367,19 +2367,19 @@
         <v>0.1939056500498176</v>
       </c>
       <c r="B17" s="39" t="n">
-        <v>-1.45</v>
+        <v>-1.83</v>
       </c>
       <c r="C17" s="39" t="n">
-        <v>-1.63</v>
+        <v>-1.98</v>
       </c>
       <c r="D17" s="39" t="n">
-        <v>-1.76</v>
+        <v>-2.09</v>
       </c>
       <c r="E17" s="39" t="n">
-        <v>-1.87</v>
+        <v>-2.18</v>
       </c>
       <c r="F17" s="39" t="n">
-        <v>-1.97</v>
+        <v>-2.25</v>
       </c>
     </row>
     <row r="18">
@@ -2387,19 +2387,19 @@
         <v>0.2039056500498176</v>
       </c>
       <c r="B18" s="39" t="n">
-        <v>-1.48</v>
+        <v>-1.85</v>
       </c>
       <c r="C18" s="39" t="n">
-        <v>-1.65</v>
+        <v>-2</v>
       </c>
       <c r="D18" s="39" t="n">
-        <v>-1.78</v>
+        <v>-2.11</v>
       </c>
       <c r="E18" s="39" t="n">
-        <v>-1.89</v>
+        <v>-2.19</v>
       </c>
       <c r="F18" s="39" t="n">
-        <v>-1.99</v>
+        <v>-2.26</v>
       </c>
     </row>
     <row r="19">
@@ -2407,19 +2407,19 @@
         <v>0.2139056500498176</v>
       </c>
       <c r="B19" s="39" t="n">
-        <v>-1.51</v>
+        <v>-1.87</v>
       </c>
       <c r="C19" s="39" t="n">
-        <v>-1.67</v>
+        <v>-2.02</v>
       </c>
       <c r="D19" s="39" t="n">
-        <v>-1.81</v>
+        <v>-2.12</v>
       </c>
       <c r="E19" s="39" t="n">
-        <v>-1.91</v>
+        <v>-2.21</v>
       </c>
       <c r="F19" s="39" t="n">
-        <v>-2</v>
+        <v>-2.28</v>
       </c>
     </row>
     <row r="20">
@@ -2427,19 +2427,19 @@
         <v>0.2239056500498176</v>
       </c>
       <c r="B20" s="39" t="n">
-        <v>-1.54</v>
+        <v>-1.89</v>
       </c>
       <c r="C20" s="39" t="n">
-        <v>-1.7</v>
+        <v>-2.03</v>
       </c>
       <c r="D20" s="39" t="n">
-        <v>-1.83</v>
+        <v>-2.14</v>
       </c>
       <c r="E20" s="39" t="n">
-        <v>-1.93</v>
+        <v>-2.22</v>
       </c>
       <c r="F20" s="39" t="n">
-        <v>-2.02</v>
+        <v>-2.29</v>
       </c>
     </row>
     <row r="21">
@@ -2447,19 +2447,19 @@
         <v>0.2339056500498176</v>
       </c>
       <c r="B21" s="39" t="n">
-        <v>-1.56</v>
+        <v>-1.91</v>
       </c>
       <c r="C21" s="39" t="n">
-        <v>-1.72</v>
+        <v>-2.05</v>
       </c>
       <c r="D21" s="39" t="n">
-        <v>-1.85</v>
+        <v>-2.15</v>
       </c>
       <c r="E21" s="39" t="n">
-        <v>-1.95</v>
+        <v>-2.23</v>
       </c>
       <c r="F21" s="39" t="n">
-        <v>-2.04</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="23">
@@ -2496,19 +2496,19 @@
         <v>-0.3</v>
       </c>
       <c r="B25" s="39" t="n">
-        <v>-3.26</v>
+        <v>0</v>
       </c>
       <c r="C25" s="39" t="n">
-        <v>-3.02</v>
+        <v>0</v>
       </c>
       <c r="D25" s="39" t="n">
-        <v>-2.77</v>
+        <v>0</v>
       </c>
       <c r="E25" s="39" t="n">
-        <v>-2.53</v>
+        <v>0</v>
       </c>
       <c r="F25" s="39" t="n">
-        <v>-2.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2516,19 +2516,19 @@
         <v>-0.15</v>
       </c>
       <c r="B26" s="39" t="n">
-        <v>-2.77</v>
+        <v>0</v>
       </c>
       <c r="C26" s="39" t="n">
-        <v>-2.53</v>
+        <v>0</v>
       </c>
       <c r="D26" s="39" t="n">
-        <v>-2.29</v>
+        <v>-2.7</v>
       </c>
       <c r="E26" s="39" t="n">
-        <v>-2.05</v>
+        <v>-2.4</v>
       </c>
       <c r="F26" s="39" t="n">
-        <v>-1.81</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="27">
@@ -2536,19 +2536,19 @@
         <v>0</v>
       </c>
       <c r="B27" s="39" t="n">
-        <v>-2.29</v>
+        <v>-2.72</v>
       </c>
       <c r="C27" s="39" t="n">
-        <v>-2.05</v>
+        <v>-2.42</v>
       </c>
       <c r="D27" s="39" t="n">
-        <v>-1.81</v>
+        <v>-2.12</v>
       </c>
       <c r="E27" s="39" t="n">
-        <v>-1.56</v>
+        <v>-1.82</v>
       </c>
       <c r="F27" s="39" t="n">
-        <v>-1.32</v>
+        <v>-1.52</v>
       </c>
     </row>
     <row r="28">
@@ -2556,19 +2556,19 @@
         <v>0.15</v>
       </c>
       <c r="B28" s="39" t="n">
-        <v>-1.81</v>
+        <v>-2.14</v>
       </c>
       <c r="C28" s="39" t="n">
-        <v>-1.56</v>
+        <v>-1.84</v>
       </c>
       <c r="D28" s="39" t="n">
-        <v>-1.32</v>
+        <v>-1.54</v>
       </c>
       <c r="E28" s="39" t="n">
-        <v>-1.08</v>
+        <v>-1.24</v>
       </c>
       <c r="F28" s="39" t="n">
-        <v>-0.84</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="29">
@@ -2576,19 +2576,19 @@
         <v>0.3</v>
       </c>
       <c r="B29" s="39" t="n">
-        <v>-1.32</v>
+        <v>-1.56</v>
       </c>
       <c r="C29" s="39" t="n">
-        <v>-1.08</v>
+        <v>-1.26</v>
       </c>
       <c r="D29" s="39" t="n">
-        <v>-0.84</v>
+        <v>-0.96</v>
       </c>
       <c r="E29" s="39" t="n">
-        <v>-0.59</v>
+        <v>-0.67</v>
       </c>
       <c r="F29" s="39" t="n">
-        <v>-0.35</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="31">
@@ -2625,13 +2625,13 @@
         <v>0.077</v>
       </c>
       <c r="B33" s="12" t="n">
-        <v>0.6493506493506493</v>
+        <v>0.9090909090909099</v>
       </c>
       <c r="C33" s="6" t="n">
-        <v>5513</v>
+        <v>1821</v>
       </c>
       <c r="D33" s="39" t="n">
-        <v>-2.02</v>
+        <v>-2.51</v>
       </c>
     </row>
     <row r="34">
@@ -2639,13 +2639,13 @@
         <v>0.08500000000000001</v>
       </c>
       <c r="B34" s="12" t="n">
-        <v>0.5882352941176471</v>
+        <v>0.8235294117647065</v>
       </c>
       <c r="C34" s="6" t="n">
-        <v>6474</v>
+        <v>3534</v>
       </c>
       <c r="D34" s="39" t="n">
-        <v>-1.89</v>
+        <v>-2.28</v>
       </c>
     </row>
     <row r="35">
@@ -2653,13 +2653,13 @@
         <v>0.09170814583433977</v>
       </c>
       <c r="B35" s="12" t="n">
-        <v>0.5452078389014566</v>
+        <v>0.7632909744620399</v>
       </c>
       <c r="C35" s="6" t="n">
-        <v>7150</v>
+        <v>4741</v>
       </c>
       <c r="D35" s="39" t="n">
-        <v>-1.81</v>
+        <v>-2.12</v>
       </c>
     </row>
     <row r="36">
@@ -2667,13 +2667,13 @@
         <v>0.12</v>
       </c>
       <c r="B36" s="12" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.5833333333333339</v>
       </c>
       <c r="C36" s="6" t="n">
-        <v>9171</v>
+        <v>8345</v>
       </c>
       <c r="D36" s="39" t="n">
-        <v>-1.54</v>
+        <v>-1.65</v>
       </c>
     </row>
     <row r="37">
@@ -2681,13 +2681,13 @@
         <v>0.15</v>
       </c>
       <c r="B37" s="12" t="n">
-        <v>0.3333333333333334</v>
+        <v>0.4666666666666671</v>
       </c>
       <c r="C37" s="6" t="n">
-        <v>10481</v>
+        <v>10681</v>
       </c>
       <c r="D37" s="39" t="n">
-        <v>-1.37</v>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="39">
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="E39" s="39" t="n">
-        <v>-1.98</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="41">
@@ -2748,7 +2748,7 @@
         <v>0.1347</v>
       </c>
       <c r="E43" s="39" t="n">
-        <v>-1.59</v>
+        <v>-1.94</v>
       </c>
     </row>
     <row r="44">
@@ -2765,7 +2765,7 @@
         <v>0.14226</v>
       </c>
       <c r="E44" s="39" t="n">
-        <v>-1.71</v>
+        <v>-2.04</v>
       </c>
     </row>
     <row r="45">
@@ -2782,7 +2782,7 @@
         <v>0.1431</v>
       </c>
       <c r="E45" s="39" t="n">
-        <v>-1.72</v>
+        <v>-2.05</v>
       </c>
     </row>
     <row r="46">
@@ -2799,7 +2799,7 @@
         <v>0.149988</v>
       </c>
       <c r="E46" s="39" t="n">
-        <v>-1.81</v>
+        <v>-2.12</v>
       </c>
     </row>
     <row r="47">
@@ -2816,7 +2816,7 @@
         <v>0.1515</v>
       </c>
       <c r="E47" s="39" t="n">
-        <v>-1.82</v>
+        <v>-2.14</v>
       </c>
     </row>
     <row r="48">
@@ -2833,7 +2833,7 @@
         <v>0.1578</v>
       </c>
       <c r="E48" s="39" t="n">
-        <v>-1.89</v>
+        <v>-2.19</v>
       </c>
     </row>
     <row r="49">
@@ -2850,7 +2850,7 @@
         <v>0.1641</v>
       </c>
       <c r="E49" s="39" t="n">
-        <v>-1.95</v>
+        <v>-2.24</v>
       </c>
     </row>
   </sheetData>
@@ -3650,14 +3650,14 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>0.61</v>
+        <v>0.48</v>
       </c>
       <c r="C9" s="8">
         <f>'Relative &amp; Normalized'!C9</f>
         <v/>
       </c>
       <c r="D9" s="7" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="E9" s="9">
         <f>Assumptions!B38</f>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
-          <t>CBE's Q4-2028 inflation target 5% + 5.5pp real-rate convention</t>
+          <t>House terminal inflation 7.00% + the 3.5pp real-rate convention (engine/macro_paths/EG.json)</t>
         </is>
       </c>
     </row>
@@ -4230,11 +4230,11 @@
         </is>
       </c>
       <c r="B26" s="18" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000006</v>
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>Standing center 5%; grid 3-7% on Sensitivity</t>
+          <t>DERIVED, not typed: zero stated real growth on the house terminal inflation of 7.00% (engine/macro_paths/EG.json)</t>
         </is>
       </c>
     </row>
